--- a/final_outputs/excel_tables/table_qr_pseudor2.xlsx
+++ b/final_outputs/excel_tables/table_qr_pseudor2.xlsx
@@ -445,7 +445,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0052</v>
+        <v>0.0023</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0057</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0052</v>
+        <v>0.0019</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0052</v>
+        <v>0.0018</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>0.9</v>
       </c>
       <c r="B6" t="n">
-        <v>0.0063</v>
+        <v>0.001</v>
       </c>
     </row>
   </sheetData>

--- a/final_outputs/excel_tables/table_qr_pseudor2.xlsx
+++ b/final_outputs/excel_tables/table_qr_pseudor2.xlsx
@@ -445,7 +445,7 @@
         <v>0.1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0023</v>
+        <v>0.009599999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -453,7 +453,7 @@
         <v>0.25</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0019</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="4">
@@ -461,7 +461,7 @@
         <v>0.5</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0019</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>0.75</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0018</v>
+        <v>0.0081</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>0.9</v>
       </c>
       <c r="B6" t="n">
-        <v>0.001</v>
+        <v>0.0134</v>
       </c>
     </row>
   </sheetData>
